--- a/Artifacts/business/saas-growth-efficiency-dashboard.xlsx
+++ b/Artifacts/business/saas-growth-efficiency-dashboard.xlsx
@@ -1366,11 +1366,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="34635909"/>
-        <c:axId val="76095754"/>
+        <c:axId val="28751373"/>
+        <c:axId val="59664438"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34635909"/>
+        <c:axId val="28751373"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1402,7 +1402,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76095754"/>
+        <c:crossAx val="59664438"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1410,7 +1410,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76095754"/>
+        <c:axId val="59664438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1486,7 +1486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34635909"/>
+        <c:crossAx val="28751373"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1775,11 +1775,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="84652422"/>
-        <c:axId val="61960735"/>
+        <c:axId val="23221431"/>
+        <c:axId val="95595480"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84652422"/>
+        <c:axId val="23221431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1811,7 +1811,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61960735"/>
+        <c:crossAx val="95595480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1819,7 +1819,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61960735"/>
+        <c:axId val="95595480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1895,7 +1895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84652422"/>
+        <c:crossAx val="23221431"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2101,11 +2101,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="58551823"/>
-        <c:axId val="61862788"/>
+        <c:axId val="39919496"/>
+        <c:axId val="41894354"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="58551823"/>
+        <c:axId val="39919496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2181,12 +2181,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61862788"/>
+        <c:crossAx val="41894354"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="61862788"/>
+        <c:axId val="41894354"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2262,7 +2262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58551823"/>
+        <c:crossAx val="39919496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2660,11 +2660,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="49413187"/>
-        <c:axId val="30312576"/>
+        <c:axId val="70256143"/>
+        <c:axId val="8176527"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="49413187"/>
+        <c:axId val="70256143"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2730,7 +2730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30312576"/>
+        <c:crossAx val="8176527"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2738,7 +2738,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30312576"/>
+        <c:axId val="8176527"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2814,7 +2814,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49413187"/>
+        <c:crossAx val="70256143"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2876,8 +2876,8 @@
       <xdr:rowOff>101160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>790200</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>967680</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
@@ -3390,7 +3390,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
   </cols>
@@ -3454,7 +3454,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -3540,7 +3540,7 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>

--- a/Artifacts/business/saas-growth-efficiency-dashboard.xlsx
+++ b/Artifacts/business/saas-growth-efficiency-dashboard.xlsx
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t xml:space="preserve">5-Metric SaaS Growth Efficiency Dashboard</t>
   </si>
@@ -849,7 +849,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -966,12 +966,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1366,11 +1362,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="28751373"/>
-        <c:axId val="59664438"/>
+        <c:axId val="32795462"/>
+        <c:axId val="99522806"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28751373"/>
+        <c:axId val="32795462"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1402,7 +1398,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59664438"/>
+        <c:crossAx val="99522806"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1410,7 +1406,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59664438"/>
+        <c:axId val="99522806"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1486,7 +1482,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28751373"/>
+        <c:crossAx val="32795462"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1775,11 +1771,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="23221431"/>
-        <c:axId val="95595480"/>
+        <c:axId val="3441047"/>
+        <c:axId val="16763787"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23221431"/>
+        <c:axId val="3441047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1811,7 +1807,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95595480"/>
+        <c:crossAx val="16763787"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1819,7 +1815,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95595480"/>
+        <c:axId val="16763787"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1895,7 +1891,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23221431"/>
+        <c:crossAx val="3441047"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2101,11 +2097,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="39919496"/>
-        <c:axId val="41894354"/>
+        <c:axId val="70219861"/>
+        <c:axId val="60879557"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="39919496"/>
+        <c:axId val="70219861"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2181,12 +2177,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41894354"/>
+        <c:crossAx val="60879557"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="41894354"/>
+        <c:axId val="60879557"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2262,7 +2258,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39919496"/>
+        <c:crossAx val="70219861"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2660,11 +2656,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="70256143"/>
-        <c:axId val="8176527"/>
+        <c:axId val="77304977"/>
+        <c:axId val="62854979"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70256143"/>
+        <c:axId val="77304977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2730,7 +2726,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8176527"/>
+        <c:crossAx val="62854979"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2738,7 +2734,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8176527"/>
+        <c:axId val="62854979"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2814,7 +2810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70256143"/>
+        <c:crossAx val="77304977"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3284,11 +3280,11 @@
         <v>15</v>
       </c>
       <c r="B8" s="11" t="str">
-        <f aca="false">'LTVCAC by Channel'!G4</f>
+        <f aca="false">'LTVCAC by Channel'!B13&amp;" "&amp;TEXT('LTVCAC by Channel'!B14,"0.0")&amp;"x"</f>
         <v>Referral 4.6x</v>
       </c>
       <c r="C8" s="6" t="str">
-        <f aca="false">'LTVCAC by Channel'!H4</f>
+        <f aca="false">IF('LTVCAC by Channel'!B14&lt;2,"KILL ZONE",IF('LTVCAC by Channel'!B14&lt;3,"BREAKEVEN","SCALE"))</f>
         <v>SCALE</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -3818,6 +3814,10 @@
         <f aca="false">B5</f>
         <v>3.15</v>
       </c>
+      <c r="D17" s="28" t="n">
+        <f aca="false">C17</f>
+        <v>3.15</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -3831,6 +3831,10 @@
         <f aca="false">B6</f>
         <v>1</v>
       </c>
+      <c r="D18" s="28" t="n">
+        <f aca="false">D17+C18</f>
+        <v>4.15</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -3844,6 +3848,10 @@
         <f aca="false">B7</f>
         <v>0.3</v>
       </c>
+      <c r="D19" s="28" t="n">
+        <f aca="false">D18-C19</f>
+        <v>3.85</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
@@ -3857,6 +3865,10 @@
         <f aca="false">B8</f>
         <v>0.13</v>
       </c>
+      <c r="D20" s="28" t="n">
+        <f aca="false">D19-C20</f>
+        <v>3.72</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -3867,6 +3879,10 @@
       </c>
       <c r="C21" s="28" t="n">
         <f aca="false">B5+B6-B7-B8</f>
+        <v>3.72</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <f aca="false">D20</f>
         <v>3.72</v>
       </c>
     </row>
@@ -3932,26 +3948,22 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="29" t="str">
-        <f aca="false">B13&amp;" "&amp;TEXT(B14,"0.0")&amp;"x"</f>
-        <v>Referral 4.6x</v>
-      </c>
-      <c r="H4" s="30" t="str">
-        <f aca="false">IF(B14&lt;2,"KILL ZONE",IF(B14&lt;3,"BREAKEVEN","SCALE"))</f>
-        <v>SCALE</v>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="30" t="n">
         <v>2100</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="30" t="n">
         <v>9500</v>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" s="31" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
         <v>4.52380952380952</v>
       </c>
@@ -3964,13 +3976,13 @@
       <c r="A6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="30" t="n">
         <v>2800</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="30" t="n">
         <v>9200</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
         <v>3.28571428571429</v>
       </c>
@@ -3983,13 +3995,13 @@
       <c r="A7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="30" t="n">
         <v>5200</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="30" t="n">
         <v>11500</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="31" t="n">
         <f aca="false">IF(B7=0,0,C7/B7)</f>
         <v>2.21153846153846</v>
       </c>
@@ -4002,13 +4014,13 @@
       <c r="A8" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="30" t="n">
         <v>6800</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="30" t="n">
         <v>12200</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="31" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
         <v>1.79411764705882</v>
       </c>
@@ -4021,13 +4033,13 @@
       <c r="A9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="30" t="n">
         <v>4600</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="31" t="n">
         <f aca="false">IF(B9=0,0,C9/B9)</f>
         <v>4.6</v>
       </c>
@@ -4040,13 +4052,13 @@
       <c r="A10" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="30" t="n">
         <v>1300</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="30" t="n">
         <v>4500</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="31" t="n">
         <f aca="false">IF(B10=0,0,C10/B10)</f>
         <v>3.46153846153846</v>
       </c>
@@ -4073,7 +4085,7 @@
       <c r="A14" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="32" t="n">
         <f aca="false">MAX(D5:D10)</f>
         <v>4.6</v>
       </c>
@@ -4136,7 +4148,7 @@
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="30" t="n">
         <v>9900</v>
       </c>
     </row>
@@ -4144,7 +4156,7 @@
       <c r="A6" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="30" t="n">
         <v>1250</v>
       </c>
     </row>
@@ -4152,7 +4164,7 @@
       <c r="A7" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="33" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -4165,7 +4177,7 @@
       <c r="A10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <f aca="false">IF(B6*B7=0,0,B5/(B6*B7))</f>
         <v>11</v>
       </c>
@@ -4183,7 +4195,7 @@
       <c r="A12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="35" t="n">
         <f aca="false">B6*B7</f>
         <v>900</v>
       </c>
@@ -4200,7 +4212,7 @@
       <c r="A16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <f aca="false">$B$12*A16-$B$5</f>
         <v>-9900</v>
       </c>
@@ -4209,7 +4221,7 @@
       <c r="A17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <f aca="false">$B$12*A17-$B$5</f>
         <v>-9000</v>
       </c>
@@ -4218,7 +4230,7 @@
       <c r="A18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <f aca="false">$B$12*A18-$B$5</f>
         <v>-8100</v>
       </c>
@@ -4227,7 +4239,7 @@
       <c r="A19" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <f aca="false">$B$12*A19-$B$5</f>
         <v>-7200</v>
       </c>
@@ -4236,7 +4248,7 @@
       <c r="A20" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <f aca="false">$B$12*A20-$B$5</f>
         <v>-6300</v>
       </c>
@@ -4245,7 +4257,7 @@
       <c r="A21" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <f aca="false">$B$12*A21-$B$5</f>
         <v>-5400</v>
       </c>
@@ -4254,7 +4266,7 @@
       <c r="A22" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <f aca="false">$B$12*A22-$B$5</f>
         <v>-4500</v>
       </c>
@@ -4263,7 +4275,7 @@
       <c r="A23" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <f aca="false">$B$12*A23-$B$5</f>
         <v>-3600</v>
       </c>
@@ -4272,7 +4284,7 @@
       <c r="A24" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <f aca="false">$B$12*A24-$B$5</f>
         <v>-2700</v>
       </c>
@@ -4281,7 +4293,7 @@
       <c r="A25" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <f aca="false">$B$12*A25-$B$5</f>
         <v>-1800</v>
       </c>
@@ -4290,7 +4302,7 @@
       <c r="A26" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <f aca="false">$B$12*A26-$B$5</f>
         <v>-900</v>
       </c>
@@ -4299,7 +4311,7 @@
       <c r="A27" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <f aca="false">$B$12*A27-$B$5</f>
         <v>0</v>
       </c>
@@ -4308,7 +4320,7 @@
       <c r="A28" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <f aca="false">$B$12*A28-$B$5</f>
         <v>900</v>
       </c>
@@ -4317,7 +4329,7 @@
       <c r="A29" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <f aca="false">$B$12*A29-$B$5</f>
         <v>1800</v>
       </c>
@@ -4326,7 +4338,7 @@
       <c r="A30" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <f aca="false">$B$12*A30-$B$5</f>
         <v>2700</v>
       </c>
@@ -4335,7 +4347,7 @@
       <c r="A31" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <f aca="false">$B$12*A31-$B$5</f>
         <v>3600</v>
       </c>
@@ -4344,7 +4356,7 @@
       <c r="A32" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <f aca="false">$B$12*A32-$B$5</f>
         <v>4500</v>
       </c>
@@ -4353,7 +4365,7 @@
       <c r="A33" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <f aca="false">$B$12*A33-$B$5</f>
         <v>5400</v>
       </c>
@@ -4362,7 +4374,7 @@
       <c r="A34" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <f aca="false">$B$12*A34-$B$5</f>
         <v>6300</v>
       </c>
@@ -4371,7 +4383,7 @@
       <c r="A35" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <f aca="false">$B$12*A35-$B$5</f>
         <v>7200</v>
       </c>
@@ -4380,7 +4392,7 @@
       <c r="A36" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <f aca="false">$B$12*A36-$B$5</f>
         <v>8100</v>
       </c>
@@ -4389,7 +4401,7 @@
       <c r="A37" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <f aca="false">$B$12*A37-$B$5</f>
         <v>9000</v>
       </c>
@@ -4398,7 +4410,7 @@
       <c r="A38" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <f aca="false">$B$12*A38-$B$5</f>
         <v>9900</v>
       </c>
@@ -4407,7 +4419,7 @@
       <c r="A39" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <f aca="false">$B$12*A39-$B$5</f>
         <v>10800</v>
       </c>
@@ -4416,7 +4428,7 @@
       <c r="A40" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <f aca="false">$B$12*A40-$B$5</f>
         <v>11700</v>
       </c>
@@ -4425,7 +4437,7 @@
       <c r="A41" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <f aca="false">$B$12*A41-$B$5</f>
         <v>12600</v>
       </c>
@@ -4434,7 +4446,7 @@
       <c r="A42" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <f aca="false">$B$12*A42-$B$5</f>
         <v>13500</v>
       </c>
@@ -4443,7 +4455,7 @@
       <c r="A43" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <f aca="false">$B$12*A43-$B$5</f>
         <v>14400</v>
       </c>
@@ -4452,7 +4464,7 @@
       <c r="A44" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <f aca="false">$B$12*A44-$B$5</f>
         <v>15300</v>
       </c>
@@ -4461,7 +4473,7 @@
       <c r="A45" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <f aca="false">$B$12*A45-$B$5</f>
         <v>16200</v>
       </c>
@@ -4470,7 +4482,7 @@
       <c r="A46" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <f aca="false">$B$12*A46-$B$5</f>
         <v>17100</v>
       </c>
@@ -4479,7 +4491,7 @@
       <c r="A47" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <f aca="false">$B$12*A47-$B$5</f>
         <v>18000</v>
       </c>
@@ -4488,7 +4500,7 @@
       <c r="A48" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <f aca="false">$B$12*A48-$B$5</f>
         <v>18900</v>
       </c>
@@ -4497,7 +4509,7 @@
       <c r="A49" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <f aca="false">$B$12*A49-$B$5</f>
         <v>19800</v>
       </c>
@@ -4506,7 +4518,7 @@
       <c r="A50" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <f aca="false">$B$12*A50-$B$5</f>
         <v>20700</v>
       </c>
@@ -4515,7 +4527,7 @@
       <c r="A51" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <f aca="false">$B$12*A51-$B$5</f>
         <v>21600</v>
       </c>
@@ -4524,7 +4536,7 @@
       <c r="A52" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <f aca="false">$B$12*A52-$B$5</f>
         <v>22500</v>
       </c>
